--- a/sektorler/Kimyasal Ürün.xlsx
+++ b/sektorler/Kimyasal Ürün.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,357 +413,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ana Ortaklığa Ait Özkaynaklar</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ödenmiş Sermaye</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net_borc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>duzeltilmis_fiyat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Satış Gelirleri</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net Faaliyet Kar/Zararı</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FAVÖK</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ana Ortaklık Payları</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>F/K</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FD/FAVÖK</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FD/NS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PD/DD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>NFK/PD_%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Sektör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>F/K (PD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>FD/FAVÖK (PD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FD/NS (PD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>PD/DD (PD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin Fiyat</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>iskonto_%</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>RNPOL</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GEDZA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1096530088</v>
+        <v>1186366071</v>
       </c>
       <c r="C2" t="n">
-        <v>30000000</v>
+        <v>46656000</v>
       </c>
       <c r="D2" t="n">
-        <v>641291655</v>
+        <v>-262816270</v>
       </c>
       <c r="E2" t="n">
-        <v>2.819999933242798</v>
+        <v>31.21999931335449</v>
       </c>
       <c r="F2" t="n">
-        <v>84599997.99728394</v>
+        <v>1456600287.963867</v>
       </c>
       <c r="G2" t="n">
-        <v>725891652.9972839</v>
+        <v>1193784017.963867</v>
       </c>
       <c r="H2" t="n">
-        <v>1579778607</v>
+        <v>1208540565</v>
       </c>
       <c r="I2" t="n">
-        <v>201181188</v>
+        <v>279091879</v>
       </c>
       <c r="J2" t="n">
-        <v>234568353</v>
+        <v>320432878</v>
       </c>
       <c r="K2" t="n">
-        <v>-31026014</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>18782965</v>
+      </c>
+      <c r="L2" t="n">
+        <v>77.54900719688649</v>
+      </c>
       <c r="M2" t="n">
-        <v>3.094584771191551</v>
+        <v>3.725535361461464</v>
       </c>
       <c r="N2" t="n">
-        <v>0.459489481488645</v>
+        <v>0.9877897792895907</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07715246387045235</v>
+        <v>1.22778316370434</v>
       </c>
       <c r="P2" t="n">
-        <v>237.8028283244864</v>
+        <v>19.16049868355671</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>6697599792.651518</v>
+      </c>
       <c r="S2" t="n">
-        <v>3357979776.819273</v>
+        <v>5897152081.213252</v>
       </c>
       <c r="T2" t="n">
-        <v>2981751975.210048</v>
+        <v>3160929103.888212</v>
       </c>
       <c r="U2" t="n">
-        <v>3593718154.520277</v>
+        <v>3935328871.311317</v>
       </c>
       <c r="V2" t="n">
-        <v>3311149968.849866</v>
+        <v>4922752462.266074</v>
       </c>
       <c r="W2" t="n">
-        <v>110.3716656283289</v>
+        <v>105.5116697159224</v>
       </c>
       <c r="X2" t="n">
-        <v>-97.44499648783139</v>
+        <v>-70.41085654562131</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>SEKUR</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KMPUR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>561520237</v>
+        <v>3823224810</v>
       </c>
       <c r="C3" t="n">
-        <v>53611826</v>
+        <v>486200000</v>
       </c>
       <c r="D3" t="n">
-        <v>644918360</v>
+        <v>4888163712</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="F3" t="n">
-        <v>428894608</v>
+        <v>10258820185.47058</v>
       </c>
       <c r="G3" t="n">
-        <v>1073812968</v>
+        <v>15146983897.47058</v>
       </c>
       <c r="H3" t="n">
-        <v>1618362873</v>
+        <v>14509027401</v>
       </c>
       <c r="I3" t="n">
-        <v>116856247</v>
+        <v>1518088520</v>
       </c>
       <c r="J3" t="n">
-        <v>174392884</v>
+        <v>1801686414</v>
       </c>
       <c r="K3" t="n">
-        <v>-13208018</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>47050927</v>
+      </c>
+      <c r="L3" t="n">
+        <v>218.0365157411369</v>
+      </c>
       <c r="M3" t="n">
-        <v>6.157435689864502</v>
+        <v>8.407114456639611</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6635180440153362</v>
+        <v>1.043969625174642</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7638097075386439</v>
+        <v>2.68328981299705</v>
       </c>
       <c r="P3" t="n">
-        <v>27.2459118907832</v>
+        <v>14.7978860390793</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>16777344733.34012</v>
+      </c>
       <c r="S3" t="n">
-        <v>2328391849.897634</v>
+        <v>26791813531.0861</v>
       </c>
       <c r="T3" t="n">
-        <v>3066613922.061775</v>
+        <v>29904874880.02593</v>
       </c>
       <c r="U3" t="n">
-        <v>1840301047.751486</v>
+        <v>12682128513.35558</v>
       </c>
       <c r="V3" t="n">
-        <v>2411768939.903632</v>
+        <v>21539040414.45193</v>
       </c>
       <c r="W3" t="n">
-        <v>44.98576377353071</v>
+        <v>44.30078242380076</v>
       </c>
       <c r="X3" t="n">
-        <v>-82.21659625415288</v>
+        <v>-52.37104351878519</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>GEDZA</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RNPOL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1074894775</v>
+        <v>1146147548</v>
       </c>
       <c r="C4" t="n">
-        <v>46656000</v>
+        <v>600000000</v>
       </c>
       <c r="D4" t="n">
-        <v>-249618334</v>
+        <v>873628850</v>
       </c>
       <c r="E4" t="n">
-        <v>29.60000038146973</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="F4" t="n">
-        <v>1381017617.797852</v>
+        <v>1547999954.223633</v>
       </c>
       <c r="G4" t="n">
-        <v>1131399283.797852</v>
+        <v>2421628804.223633</v>
       </c>
       <c r="H4" t="n">
-        <v>1066938262</v>
+        <v>1994330107</v>
       </c>
       <c r="I4" t="n">
-        <v>254682937</v>
+        <v>228985183</v>
       </c>
       <c r="J4" t="n">
-        <v>297879200</v>
+        <v>273969763</v>
       </c>
       <c r="K4" t="n">
-        <v>16355260</v>
-      </c>
-      <c r="L4" t="n">
-        <v>84.43874434266722</v>
-      </c>
+        <v>-57934066</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>3.798181557483206</v>
+        <v>8.839036752474151</v>
       </c>
       <c r="N4" t="n">
-        <v>1.060416824565854</v>
+        <v>1.214256755049646</v>
       </c>
       <c r="O4" t="n">
-        <v>1.284793311789846</v>
+        <v>1.350611408561538</v>
       </c>
       <c r="P4" t="n">
-        <v>18.44168631288812</v>
+        <v>14.79232492063236</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-20658037132.53256</v>
+      </c>
       <c r="S4" t="n">
-        <v>5328307592.193238</v>
+        <v>3943722154.975549</v>
       </c>
       <c r="T4" t="n">
-        <v>2696520613.115671</v>
+        <v>3908828475.382662</v>
       </c>
       <c r="U4" t="n">
-        <v>3522811557.466801</v>
+        <v>3801918856.820606</v>
       </c>
       <c r="V4" t="n">
-        <v>3849213254.25857</v>
-      </c>
-      <c r="W4" t="n">
-        <v>82.50199876240076</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-64.12208088834868</v>
-      </c>
+        <v>-2250891911.338436</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>FRMPL</t>
         </is>
@@ -790,13 +782,13 @@
         <v>-18471913</v>
       </c>
       <c r="E5" t="n">
-        <v>32.97999954223633</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="F5" t="n">
-        <v>5276799926.757812</v>
+        <v>5824000244.140625</v>
       </c>
       <c r="G5" t="n">
-        <v>5258328013.757812</v>
+        <v>5805528331.140625</v>
       </c>
       <c r="H5" t="n">
         <v>4612011904</v>
@@ -811,756 +803,776 @@
         <v>208896291</v>
       </c>
       <c r="L5" t="n">
-        <v>25.26038112738829</v>
+        <v>27.87986429180126</v>
       </c>
       <c r="M5" t="n">
-        <v>5.519666881231797</v>
+        <v>6.094063050766105</v>
       </c>
       <c r="N5" t="n">
-        <v>1.140137563217749</v>
+        <v>1.25878433360189</v>
       </c>
       <c r="O5" t="n">
-        <v>1.466615361427902</v>
+        <v>1.618702308515348</v>
       </c>
       <c r="P5" t="n">
-        <v>15.14102526322048</v>
+        <v>13.71843366256405</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>74487907275.94238</v>
+      </c>
       <c r="S5" t="n">
-        <v>16260724793.68286</v>
+        <v>16769461274.76715</v>
       </c>
       <c r="T5" t="n">
-        <v>10595599794.84384</v>
+        <v>11078200709.96232</v>
       </c>
       <c r="U5" t="n">
-        <v>11791739032.88629</v>
+        <v>11934843056.67012</v>
       </c>
       <c r="V5" t="n">
-        <v>12882687873.80433</v>
+        <v>28567603079.33549</v>
       </c>
       <c r="W5" t="n">
-        <v>80.51679921127706</v>
+        <v>178.5475192458468</v>
       </c>
       <c r="X5" t="n">
-        <v>-59.03960432443866</v>
+        <v>-79.613269520839</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>KMPUR</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SEKUR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3437055733</v>
+        <v>595998092</v>
       </c>
       <c r="C6" t="n">
-        <v>486200000</v>
+        <v>187641391</v>
       </c>
       <c r="D6" t="n">
-        <v>4411553567</v>
+        <v>616909742</v>
       </c>
       <c r="E6" t="n">
-        <v>20.78000068664551</v>
+        <v>7.960000038146973</v>
       </c>
       <c r="F6" t="n">
-        <v>10103236333.84705</v>
+        <v>1493625479.517951</v>
       </c>
       <c r="G6" t="n">
-        <v>14514789900.84705</v>
+        <v>2110535221.517951</v>
       </c>
       <c r="H6" t="n">
-        <v>13421832888</v>
+        <v>1871551079</v>
       </c>
       <c r="I6" t="n">
-        <v>1393670477</v>
+        <v>189613921</v>
       </c>
       <c r="J6" t="n">
-        <v>1642213507</v>
+        <v>255123407</v>
       </c>
       <c r="K6" t="n">
-        <v>-353662780</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>41400575</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36.07740905815803</v>
+      </c>
       <c r="M6" t="n">
-        <v>8.838552258264336</v>
+        <v>8.27260519266251</v>
       </c>
       <c r="N6" t="n">
-        <v>1.081431278571813</v>
+        <v>1.127693091147501</v>
       </c>
       <c r="O6" t="n">
-        <v>2.939503202361091</v>
+        <v>2.506091042180637</v>
       </c>
       <c r="P6" t="n">
-        <v>13.79429749981239</v>
+        <v>12.69487723664138</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>14762551201.88179</v>
+      </c>
       <c r="S6" t="n">
-        <v>23587353700.31086</v>
+        <v>3869056109.290809</v>
       </c>
       <c r="T6" t="n">
-        <v>26369902730.19376</v>
+        <v>3871120166.476619</v>
       </c>
       <c r="U6" t="n">
-        <v>11264451127.1998</v>
+        <v>1977002340.194251</v>
       </c>
       <c r="V6" t="n">
-        <v>20407235852.56814</v>
+        <v>6119932454.460868</v>
       </c>
       <c r="W6" t="n">
-        <v>41.97292441910354</v>
+        <v>32.61504522987078</v>
       </c>
       <c r="X6" t="n">
-        <v>-50.49189215610694</v>
+        <v>-75.59408554535213</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>MERCN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2438408137</v>
+        <v>2673958636</v>
       </c>
       <c r="C7" t="n">
         <v>190370946</v>
       </c>
       <c r="D7" t="n">
-        <v>812898644</v>
+        <v>1264757565</v>
       </c>
       <c r="E7" t="n">
-        <v>24.34000015258789</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="F7" t="n">
-        <v>4633628854.688301</v>
+        <v>4195775824.129807</v>
       </c>
       <c r="G7" t="n">
-        <v>5446527498.688301</v>
+        <v>5460533389.129807</v>
       </c>
       <c r="H7" t="n">
-        <v>2900312489</v>
+        <v>3181382748</v>
       </c>
       <c r="I7" t="n">
-        <v>436655469</v>
+        <v>478861580</v>
       </c>
       <c r="J7" t="n">
-        <v>517996929</v>
+        <v>563420449</v>
       </c>
       <c r="K7" t="n">
-        <v>141906215</v>
+        <v>165069602</v>
       </c>
       <c r="L7" t="n">
-        <v>32.65275488242923</v>
+        <v>25.41822221228719</v>
       </c>
       <c r="M7" t="n">
-        <v>10.5145941872723</v>
+        <v>9.691755772836364</v>
       </c>
       <c r="N7" t="n">
-        <v>1.877910576651763</v>
+        <v>1.716402527348403</v>
       </c>
       <c r="O7" t="n">
-        <v>1.900267959402852</v>
+        <v>1.569125179290846</v>
       </c>
       <c r="P7" t="n">
-        <v>9.423617702099564</v>
+        <v>11.41294483003783</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>58860256201.73751</v>
+      </c>
       <c r="S7" t="n">
-        <v>8018686237.016819</v>
+        <v>8642153462.308969</v>
       </c>
       <c r="T7" t="n">
-        <v>5838640149.049437</v>
+        <v>6364283973.61757</v>
       </c>
       <c r="U7" t="n">
-        <v>7991528628.320563</v>
+        <v>8869864772.91378</v>
       </c>
       <c r="V7" t="n">
-        <v>7282951671.462273</v>
+        <v>20684139602.64445</v>
       </c>
       <c r="W7" t="n">
-        <v>38.25663434725104</v>
+        <v>108.6517666547943</v>
       </c>
       <c r="X7" t="n">
-        <v>-36.37704788231885</v>
+        <v>-79.71500915806341</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>BNTAS</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1693692129</v>
+        <v>6697968298</v>
       </c>
       <c r="C8" t="n">
-        <v>241875000</v>
+        <v>609000000</v>
       </c>
       <c r="D8" t="n">
-        <v>-586861199</v>
+        <v>-704899657</v>
       </c>
       <c r="E8" t="n">
-        <v>6.739999771118164</v>
+        <v>13.96000003814697</v>
       </c>
       <c r="F8" t="n">
-        <v>1630237444.639206</v>
+        <v>8501640023.231506</v>
       </c>
       <c r="G8" t="n">
-        <v>1043376245.639206</v>
+        <v>7796740366.231506</v>
       </c>
       <c r="H8" t="n">
-        <v>1451429259</v>
+        <v>6424082090</v>
       </c>
       <c r="I8" t="n">
-        <v>125962539</v>
+        <v>940444314</v>
       </c>
       <c r="J8" t="n">
-        <v>202954052</v>
+        <v>1085594632</v>
       </c>
       <c r="K8" t="n">
-        <v>253687631</v>
+        <v>326227070</v>
       </c>
       <c r="L8" t="n">
-        <v>6.426160543235969</v>
+        <v>26.06049836155996</v>
       </c>
       <c r="M8" t="n">
-        <v>5.140948088285549</v>
+        <v>7.18199974134683</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7188612460231559</v>
+        <v>1.213673838067581</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9625346996220268</v>
+        <v>1.269286393273924</v>
       </c>
       <c r="P8" t="n">
-        <v>7.726637577501923</v>
+        <v>11.06191642353887</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>116325529882.4926</v>
+      </c>
       <c r="S8" t="n">
-        <v>4047124835.397546</v>
+        <v>19793467439.7931</v>
       </c>
       <c r="T8" t="n">
-        <v>3915550110.357337</v>
+        <v>16110021578.56364</v>
       </c>
       <c r="U8" t="n">
-        <v>5550830039.928097</v>
+        <v>22218022469.26136</v>
       </c>
       <c r="V8" t="n">
-        <v>4504501661.894326</v>
+        <v>43611760342.52766</v>
       </c>
       <c r="W8" t="n">
-        <v>18.62326268483442</v>
+        <v>71.61208594832129</v>
       </c>
       <c r="X8" t="n">
-        <v>-63.80870589015113</v>
+        <v>-80.5060837800184</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>SANFM</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>571899813</v>
+        <v>1693692129</v>
       </c>
       <c r="C9" t="n">
-        <v>375000000</v>
+        <v>241875000</v>
       </c>
       <c r="D9" t="n">
-        <v>376179645</v>
+        <v>-586861199</v>
       </c>
       <c r="E9" t="n">
-        <v>7.579999923706055</v>
+        <v>7.010000228881836</v>
       </c>
       <c r="F9" t="n">
-        <v>2842499971.389771</v>
+        <v>1695543805.360794</v>
       </c>
       <c r="G9" t="n">
-        <v>3218679616.389771</v>
+        <v>1108682606.360794</v>
       </c>
       <c r="H9" t="n">
-        <v>1150867542</v>
+        <v>1451429259</v>
       </c>
       <c r="I9" t="n">
-        <v>108066783</v>
+        <v>125962539</v>
       </c>
       <c r="J9" t="n">
-        <v>164827658</v>
+        <v>202954052</v>
       </c>
       <c r="K9" t="n">
-        <v>1801854</v>
+        <v>253687631</v>
       </c>
       <c r="L9" t="n">
-        <v>1577.541782735877</v>
+        <v>6.683588784668789</v>
       </c>
       <c r="M9" t="n">
-        <v>19.52754565250069</v>
+        <v>5.462727131758838</v>
       </c>
       <c r="N9" t="n">
-        <v>2.796742021932678</v>
+        <v>0.7638557645755673</v>
       </c>
       <c r="O9" t="n">
-        <v>4.970276098673546</v>
+        <v>1.001093278010265</v>
       </c>
       <c r="P9" t="n">
-        <v>3.801821779690763</v>
+        <v>7.429034779387282</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>90459532069.82257</v>
+      </c>
       <c r="S9" t="n">
-        <v>2434048313.641452</v>
+        <v>4155506496.423059</v>
       </c>
       <c r="T9" t="n">
-        <v>2263204949.007605</v>
+        <v>4067427664.70962</v>
       </c>
       <c r="U9" t="n">
-        <v>1874318601.045858</v>
+        <v>5618194667.981559</v>
       </c>
       <c r="V9" t="n">
-        <v>2190523954.564972</v>
+        <v>26075165224.7342</v>
       </c>
       <c r="W9" t="n">
-        <v>5.841397212173258</v>
+        <v>107.8043006707357</v>
       </c>
       <c r="X9" t="n">
-        <v>29.76347350441453</v>
+        <v>-93.49747627388973</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ALKIM</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SANFM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4254475681</v>
+        <v>633089921</v>
       </c>
       <c r="C10" t="n">
-        <v>300000000</v>
+        <v>375000000</v>
       </c>
       <c r="D10" t="n">
-        <v>-27559090</v>
+        <v>401718428</v>
       </c>
       <c r="E10" t="n">
-        <v>19.8799991607666</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="F10" t="n">
-        <v>5963999748.22998</v>
+        <v>3018750071.525574</v>
       </c>
       <c r="G10" t="n">
-        <v>5936440658.22998</v>
+        <v>3420468499.525574</v>
       </c>
       <c r="H10" t="n">
-        <v>5099297532</v>
+        <v>1320417435</v>
       </c>
       <c r="I10" t="n">
-        <v>134162670</v>
+        <v>88705174</v>
       </c>
       <c r="J10" t="n">
-        <v>400284683</v>
+        <v>164557282</v>
       </c>
       <c r="K10" t="n">
-        <v>-408293249</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>30574710</v>
+      </c>
+      <c r="L10" t="n">
+        <v>98.73356350806185</v>
+      </c>
       <c r="M10" t="n">
-        <v>14.83054663430622</v>
+        <v>20.78588354130432</v>
       </c>
       <c r="N10" t="n">
-        <v>1.164168323377209</v>
+        <v>2.590444816055896</v>
       </c>
       <c r="O10" t="n">
-        <v>1.401817802100625</v>
+        <v>4.768280099543038</v>
       </c>
       <c r="P10" t="n">
-        <v>2.249541845467336</v>
+        <v>2.938473603254323</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>10902281474.53718</v>
+      </c>
       <c r="S10" t="n">
-        <v>6852209887.274148</v>
+        <v>2491776748.760601</v>
       </c>
       <c r="T10" t="n">
-        <v>11722221468.63697</v>
+        <v>2764678154.19768</v>
       </c>
       <c r="U10" t="n">
-        <v>13943426322.81215</v>
+        <v>2100040708.469908</v>
       </c>
       <c r="V10" t="n">
-        <v>10839285892.90775</v>
+        <v>4564694271.491343</v>
       </c>
       <c r="W10" t="n">
-        <v>36.13095297635918</v>
+        <v>12.17251805731025</v>
       </c>
       <c r="X10" t="n">
-        <v>-44.97792744693374</v>
+        <v>-33.86742042333297</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>TMPOL</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>834886202</v>
+        <v>638570889</v>
       </c>
       <c r="C11" t="n">
-        <v>14175000</v>
+        <v>10721700</v>
       </c>
       <c r="D11" t="n">
-        <v>660687907</v>
+        <v>146558498</v>
       </c>
       <c r="E11" t="n">
-        <v>461.75</v>
+        <v>158.1999969482422</v>
       </c>
       <c r="F11" t="n">
-        <v>6545306250</v>
+        <v>1696172907.279968</v>
       </c>
       <c r="G11" t="n">
-        <v>7205994157</v>
+        <v>1842731405.279968</v>
       </c>
       <c r="H11" t="n">
-        <v>1260512358</v>
+        <v>827410173</v>
       </c>
       <c r="I11" t="n">
-        <v>89777279</v>
+        <v>36737798</v>
       </c>
       <c r="J11" t="n">
-        <v>180085402</v>
+        <v>80510962</v>
       </c>
       <c r="K11" t="n">
-        <v>-54079797</v>
+        <v>-29809440</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>40.01431585776175</v>
+        <v>22.88795661490131</v>
       </c>
       <c r="N11" t="n">
-        <v>5.716718373498089</v>
+        <v>2.227107504127784</v>
       </c>
       <c r="O11" t="n">
-        <v>7.839758561490755</v>
+        <v>2.656201428060978</v>
       </c>
       <c r="P11" t="n">
-        <v>1.371628394011357</v>
+        <v>2.165922934054747</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>-10629402714.80343</v>
+      </c>
       <c r="S11" t="n">
-        <v>2409676847.218525</v>
+        <v>1269107082.957736</v>
       </c>
       <c r="T11" t="n">
-        <v>2230154676.395578</v>
+        <v>1837593387.924463</v>
       </c>
       <c r="U11" t="n">
-        <v>2736218307.11305</v>
+        <v>2118221784.39612</v>
       </c>
       <c r="V11" t="n">
-        <v>2458683276.909051</v>
-      </c>
-      <c r="W11" t="n">
-        <v>173.4520830270936</v>
-      </c>
-      <c r="X11" t="n">
-        <v>166.2118505246626</v>
-      </c>
+        <v>-1351120114.881279</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ISKPL</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TMPOL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2851970091</v>
+        <v>879240094</v>
       </c>
       <c r="C12" t="n">
-        <v>1500000000</v>
+        <v>14175000</v>
       </c>
       <c r="D12" t="n">
-        <v>1464783619</v>
+        <v>586946472</v>
       </c>
       <c r="E12" t="n">
-        <v>20.95999908447266</v>
+        <v>330.75</v>
       </c>
       <c r="F12" t="n">
-        <v>31439998626.70898</v>
+        <v>4688381250</v>
       </c>
       <c r="G12" t="n">
-        <v>32904782245.70898</v>
+        <v>5275327722</v>
       </c>
       <c r="H12" t="n">
-        <v>2527986916</v>
+        <v>1381101005</v>
       </c>
       <c r="I12" t="n">
-        <v>347792924</v>
+        <v>85437012</v>
       </c>
       <c r="J12" t="n">
-        <v>562213836</v>
+        <v>182953333</v>
       </c>
       <c r="K12" t="n">
-        <v>222810994</v>
-      </c>
-      <c r="L12" t="n">
-        <v>141.1061369202858</v>
-      </c>
+        <v>-107481171</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>58.52716553512387</v>
+        <v>28.83428049927901</v>
       </c>
       <c r="N12" t="n">
-        <v>13.01619958451912</v>
+        <v>3.819653814530386</v>
       </c>
       <c r="O12" t="n">
-        <v>11.02395804427424</v>
+        <v>5.332310573634964</v>
       </c>
       <c r="P12" t="n">
-        <v>1.106211638649825</v>
+        <v>1.822313661031726</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>-38325465047.90604</v>
+      </c>
       <c r="S12" t="n">
-        <v>8120677096.95739</v>
+        <v>2630015914.433777</v>
       </c>
       <c r="T12" t="n">
-        <v>4332868566.366087</v>
+        <v>2724970945.920024</v>
       </c>
       <c r="U12" t="n">
-        <v>9346917886.101404</v>
+        <v>2916552497.001304</v>
       </c>
       <c r="V12" t="n">
-        <v>7266821183.141627</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.844547455427752</v>
-      </c>
-      <c r="X12" t="n">
-        <v>332.6513317769117</v>
-      </c>
+        <v>-7513481422.637733</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ACSEL</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ISKPL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>575012082</v>
+        <v>3131402465</v>
       </c>
       <c r="C13" t="n">
-        <v>10721700</v>
+        <v>1500000000</v>
       </c>
       <c r="D13" t="n">
-        <v>168213818</v>
+        <v>1804639604</v>
       </c>
       <c r="E13" t="n">
-        <v>122.3000030517578</v>
+        <v>21.65999984741211</v>
       </c>
       <c r="F13" t="n">
-        <v>1311263942.720032</v>
+        <v>32489999771.11816</v>
       </c>
       <c r="G13" t="n">
-        <v>1479477760.720032</v>
+        <v>34294639375.11816</v>
       </c>
       <c r="H13" t="n">
-        <v>685775803</v>
+        <v>2888807059</v>
       </c>
       <c r="I13" t="n">
-        <v>-14422827</v>
+        <v>414413302</v>
       </c>
       <c r="J13" t="n">
-        <v>23908848</v>
+        <v>667982559</v>
       </c>
       <c r="K13" t="n">
-        <v>-67173607</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>246424539</v>
+      </c>
+      <c r="L13" t="n">
+        <v>131.8456347852523</v>
+      </c>
       <c r="M13" t="n">
-        <v>61.87992665811552</v>
+        <v>51.34062096839592</v>
       </c>
       <c r="N13" t="n">
-        <v>2.157378190143043</v>
+        <v>11.87155759270047</v>
       </c>
       <c r="O13" t="n">
-        <v>2.280411114422517</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>10.37554263122104</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.275510326006191</v>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>87869670273.60408</v>
+      </c>
       <c r="S13" t="n">
-        <v>239419912.4295663</v>
+        <v>9940840687.94298</v>
       </c>
       <c r="T13" t="n">
-        <v>1404535454.462664</v>
+        <v>5122797550.180059</v>
       </c>
       <c r="U13" t="n">
-        <v>1884518610.812531</v>
+        <v>10387264799.15483</v>
       </c>
       <c r="V13" t="n">
-        <v>1176157992.568254</v>
+        <v>28330143327.72049</v>
       </c>
       <c r="W13" t="n">
-        <v>109.6988343796463</v>
+        <v>18.88676221848032</v>
       </c>
       <c r="X13" t="n">
-        <v>11.48705794676115</v>
+        <v>14.68349946301661</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>BAHKM</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POLTK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1212231670</v>
+        <v>336306420</v>
       </c>
       <c r="C14" t="n">
-        <v>55000000</v>
+        <v>3750000</v>
       </c>
       <c r="D14" t="n">
-        <v>-173915700</v>
+        <v>-2997347</v>
       </c>
       <c r="E14" t="n">
-        <v>121.0999984741211</v>
+        <v>5200</v>
       </c>
       <c r="F14" t="n">
-        <v>6660499916.07666</v>
+        <v>19500000000</v>
       </c>
       <c r="G14" t="n">
-        <v>6486584216.07666</v>
+        <v>19497002653</v>
       </c>
       <c r="H14" t="n">
-        <v>979867542</v>
+        <v>1070598060</v>
       </c>
       <c r="I14" t="n">
-        <v>-113720397</v>
+        <v>75956225</v>
       </c>
       <c r="J14" t="n">
-        <v>-87675631</v>
+        <v>116343317</v>
       </c>
       <c r="K14" t="n">
-        <v>-274371482</v>
+        <v>-20378923</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>167.5816295748212</v>
+      </c>
       <c r="N14" t="n">
-        <v>6.619858233937358</v>
+        <v>18.21131887068803</v>
       </c>
       <c r="O14" t="n">
-        <v>5.494411737384043</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
+        <v>57.98283601008865</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3895191025641025</v>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>-7266683958.536964</v>
+      </c>
       <c r="S14" t="n">
-        <v>-1320909334.326042</v>
+        <v>2048721623.047714</v>
       </c>
       <c r="T14" t="n">
-        <v>2421131126.745348</v>
+        <v>2570320337.620362</v>
       </c>
       <c r="U14" t="n">
-        <v>3972913290.422573</v>
+        <v>1115571657.505156</v>
       </c>
       <c r="V14" t="n">
-        <v>1691045027.61396</v>
-      </c>
-      <c r="W14" t="n">
-        <v>30.74627322934472</v>
-      </c>
-      <c r="X14" t="n">
-        <v>293.8688684992931</v>
-      </c>
+        <v>-383017585.0909331</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OZRDN</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ALKIM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>324365627</v>
+        <v>4481586649</v>
       </c>
       <c r="C15" t="n">
-        <v>73500000</v>
+        <v>300000000</v>
       </c>
       <c r="D15" t="n">
-        <v>-79840851</v>
+        <v>-91521153</v>
       </c>
       <c r="E15" t="n">
-        <v>35.58000183105469</v>
+        <v>18.45000076293945</v>
       </c>
       <c r="F15" t="n">
-        <v>2615130134.58252</v>
+        <v>5535000228.881836</v>
       </c>
       <c r="G15" t="n">
-        <v>2535289283.58252</v>
+        <v>5443479075.881836</v>
       </c>
       <c r="H15" t="n">
-        <v>554402128</v>
+        <v>5522752567</v>
       </c>
       <c r="I15" t="n">
-        <v>-33335406</v>
+        <v>-28071965</v>
       </c>
       <c r="J15" t="n">
-        <v>-10298852</v>
+        <v>263808234</v>
       </c>
       <c r="K15" t="n">
-        <v>-58581185</v>
+        <v>-501431571</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>20.63422734516253</v>
+      </c>
       <c r="N15" t="n">
-        <v>4.573015065307469</v>
+        <v>0.9856460179672278</v>
       </c>
       <c r="O15" t="n">
-        <v>8.062291182852491</v>
+        <v>1.235053712532121</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
@@ -1568,71 +1580,67 @@
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>-178799672254.0092</v>
+      </c>
       <c r="S15" t="n">
-        <v>-95749351.41803369</v>
+        <v>4730196776.414416</v>
       </c>
       <c r="T15" t="n">
-        <v>1351299452.556627</v>
+        <v>13335230595.89468</v>
       </c>
       <c r="U15" t="n">
-        <v>1063061246.753726</v>
+        <v>14865999424.80405</v>
       </c>
       <c r="V15" t="n">
-        <v>772870449.2974396</v>
-      </c>
-      <c r="W15" t="n">
-        <v>10.51524420812843</v>
-      </c>
-      <c r="X15" t="n">
-        <v>238.3659107370122</v>
-      </c>
+        <v>-36467061364.224</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SEYKM</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BAHKM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>495021011</v>
+        <v>1321868358</v>
       </c>
       <c r="C16" t="n">
-        <v>200000000</v>
+        <v>55000000</v>
       </c>
       <c r="D16" t="n">
-        <v>-253643462</v>
+        <v>-365698729</v>
       </c>
       <c r="E16" t="n">
-        <v>5.409999847412109</v>
+        <v>116.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1081999969.482422</v>
+        <v>6407500000</v>
       </c>
       <c r="G16" t="n">
-        <v>828356507.4824219</v>
+        <v>6041801271</v>
       </c>
       <c r="H16" t="n">
-        <v>242207227</v>
+        <v>985333242</v>
       </c>
       <c r="I16" t="n">
-        <v>-9204826</v>
+        <v>-131234574</v>
       </c>
       <c r="J16" t="n">
-        <v>10412493</v>
+        <v>-106297188</v>
       </c>
       <c r="K16" t="n">
-        <v>-39473161</v>
+        <v>-260031489</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>79.55409981859502</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>3.420032167258254</v>
+        <v>6.131733928651927</v>
       </c>
       <c r="O16" t="n">
-        <v>2.185765746178442</v>
+        <v>4.847305680041099</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
@@ -1640,147 +1648,291 @@
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>-92721614868.00755</v>
+      </c>
       <c r="S16" t="n">
-        <v>431171185.8226512</v>
+        <v>-1503379302.935498</v>
       </c>
       <c r="T16" t="n">
-        <v>809118353.9151486</v>
+        <v>2728554388.956172</v>
       </c>
       <c r="U16" t="n">
-        <v>1622359489.783268</v>
+        <v>4384807388.267161</v>
       </c>
       <c r="V16" t="n">
-        <v>954216343.1736892</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.771081715868446</v>
-      </c>
-      <c r="X16" t="n">
-        <v>13.39147324638446</v>
-      </c>
+        <v>-21777908098.42993</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SEKTÖR TOPLAM</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OZRDN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25019907267</v>
+        <v>353515478</v>
       </c>
       <c r="C17" t="n">
-        <v>3737110472</v>
+        <v>73500000</v>
       </c>
       <c r="D17" t="n">
-        <v>7790616666</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>-93725905</v>
+      </c>
+      <c r="E17" t="n">
+        <v>35.43999862670898</v>
+      </c>
       <c r="F17" t="n">
-        <v>81999113342.91788</v>
+        <v>2604839899.06311</v>
       </c>
       <c r="G17" t="n">
-        <v>89789730008.91788</v>
+        <v>2511113994.06311</v>
       </c>
       <c r="H17" t="n">
-        <v>39151583330</v>
+        <v>595417146</v>
       </c>
       <c r="I17" t="n">
-        <v>3837086667</v>
+        <v>-25824628</v>
       </c>
       <c r="J17" t="n">
-        <v>5266416507</v>
+        <v>-2075419</v>
       </c>
       <c r="K17" t="n">
-        <v>-454411048</v>
+        <v>-50939547</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>17.04949274133017</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>2.293386943054134</v>
+        <v>4.217402892967933</v>
       </c>
       <c r="O17" t="n">
-        <v>3.277354806629143</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.0467942458225544</v>
-      </c>
+        <v>7.368389960744832</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>-18163942669.59249</v>
+      </c>
+      <c r="S17" t="n">
+        <v>57232747.15690128</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1521552262.106756</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1172656316.659633</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-3853125335.917299</v>
+      </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SEYKM</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>573457342</v>
+      </c>
+      <c r="C18" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-269967329</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.429999828338623</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1085999965.667725</v>
+      </c>
+      <c r="G18" t="n">
+        <v>816032636.6677246</v>
+      </c>
+      <c r="H18" t="n">
+        <v>274933689</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-10259332</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11592549</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3990134</v>
+      </c>
+      <c r="L18" t="n">
+        <v>272.1713019331493</v>
+      </c>
+      <c r="M18" t="n">
+        <v>70.39285636556072</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.968107108429788</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.893776373810425</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Kimyasal Ürün</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1422795636.953579</v>
+      </c>
+      <c r="S18" t="n">
+        <v>473805069.9385075</v>
+      </c>
+      <c r="T18" t="n">
+        <v>929265722.1483759</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1902231772.808385</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1182024550.462212</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5.910122752311058</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-8.123738610753739</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SEKTÖR TOPLAM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>33764337191</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5053890037</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8186363369</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>112000649897.5751</v>
+      </c>
+      <c r="G19" t="n">
+        <v>120187013266.5751</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50119125529</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5065868558</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6835210369</v>
+      </c>
+      <c r="K19" t="n">
+        <v>314098237</v>
+      </c>
+      <c r="L19" t="n">
+        <v>356.5784098863794</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17.58351342215655</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.398026940773984</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.317128639724321</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04523070680958324</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Kimyasal Ürün</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>SEKTÖR Median</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1096530088</v>
-      </c>
-      <c r="C18" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>168213818</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>2842499971.389771</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3218679616.389771</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="B20" t="n">
+        <v>1186366071</v>
+      </c>
+      <c r="C20" t="n">
+        <v>190370946</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-2997347</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>4195775824.129807</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5275327722</v>
+      </c>
+      <c r="H20" t="n">
         <v>1451429259</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I20" t="n">
         <v>125962539</v>
       </c>
-      <c r="J18" t="n">
-        <v>202954052</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-31026014</v>
-      </c>
-      <c r="L18" t="n">
-        <v>58.54574961254822</v>
-      </c>
-      <c r="M18" t="n">
-        <v>10.5145941872723</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.877910576651763</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.185765746178442</v>
-      </c>
-      <c r="P18" t="n">
-        <v>9.423617702099564</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="J20" t="n">
+        <v>255123407</v>
+      </c>
+      <c r="K20" t="n">
+        <v>18782965</v>
+      </c>
+      <c r="L20" t="n">
+        <v>56.81320812752226</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9.691755772836364</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.716402527348403</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.506091042180637</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11.06191642353887</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Kimyasal Ürün</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
